--- a/data/trans_camb/IP16A05-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A05-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 23,52</t>
+          <t>-0,8; 24,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 28,73</t>
+          <t>0,34; 27,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 34,78</t>
+          <t>-0,24; 34,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 13,72</t>
+          <t>-12,1; 13,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 22,48</t>
+          <t>-8,87; 23,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,13; -1,04</t>
+          <t>-22,88; -0,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 14,84</t>
+          <t>-2,13; 15,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 21,27</t>
+          <t>0,71; 21,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 11,77</t>
+          <t>-7,79; 11,42</t>
         </is>
       </c>
     </row>
@@ -783,27 +783,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-30,44; 1104,55</t>
+          <t>-26,14; 1499,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,9; 1202,68</t>
+          <t>-11,67; 1593,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-51,01; 1589,08</t>
+          <t>-41,87; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-69,48; 317,9</t>
+          <t>-72,23; 325,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-52,55; 393,81</t>
+          <t>-58,73; 453,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,17; 333,14</t>
+          <t>-22,22; 335,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 399,12</t>
+          <t>-4,81; 428,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-70,68; 267,44</t>
+          <t>-67,54; 231,39</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 18,4</t>
+          <t>-6,16; 18,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 12,28</t>
+          <t>-11,24; 13,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 19,76</t>
+          <t>-10,96; 19,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 13,84</t>
+          <t>-8,87; 13,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 10,34</t>
+          <t>-11,51; 10,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 10,68</t>
+          <t>-12,44; 9,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 11,72</t>
+          <t>-4,81; 11,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 7,62</t>
+          <t>-8,23; 7,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 9,91</t>
+          <t>-8,93; 9,96</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-37,46; 232,78</t>
+          <t>-38,06; 252,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-55,58; 172,56</t>
+          <t>-58,86; 167,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-59,65; 272,18</t>
+          <t>-59,2; 214,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-46,5; 168,51</t>
+          <t>-46,34; 159,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-65,41; 120,1</t>
+          <t>-64,63; 125,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-64,21; 152,78</t>
+          <t>-67,1; 110,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,77; 120,35</t>
+          <t>-27,33; 123,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,69; 73,52</t>
+          <t>-46,99; 72,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-49,71; 93,94</t>
+          <t>-51,18; 96,64</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 24,98</t>
+          <t>-2,73; 25,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,82; 6,76</t>
+          <t>-12,94; 6,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 12,83</t>
+          <t>-8,75; 13,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,41; 15,77</t>
+          <t>-16,17; 15,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 15,46</t>
+          <t>-12,92; 16,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,41; 6,16</t>
+          <t>-18,64; 6,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 16,29</t>
+          <t>-3,57; 15,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 8,59</t>
+          <t>-9,69; 7,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 6,62</t>
+          <t>-10,04; 6,68</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-60,82; —</t>
+          <t>-48,28; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-85,57; —</t>
+          <t>-81,84; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-89,09; 439,01</t>
+          <t>-86,23; 380,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-71,09; 326,82</t>
+          <t>-73,99; 390,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 193,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-45,14; 368,22</t>
+          <t>-34,42; 393,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-65,86; 275,37</t>
+          <t>-70,43; 218,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-74,75; 188,9</t>
+          <t>-75,52; 168,97</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 24,54</t>
+          <t>-3,63; 24,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 14,86</t>
+          <t>-9,3; 14,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,36; 1,04</t>
+          <t>-16,1; 0,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 12,4</t>
+          <t>-4,9; 11,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 19,78</t>
+          <t>-4,72; 17,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 1,12</t>
+          <t>-10,02; 1,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 14,59</t>
+          <t>-1,5; 14,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 10,71</t>
+          <t>-4,65; 11,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,85; -0,01</t>
+          <t>-9,04; 0,05</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-45,8; —</t>
+          <t>-57,9; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-28,5; 779,72</t>
+          <t>-31,43; 840,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-79,73; 433,38</t>
+          <t>-76,33; 722,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 32,34</t>
+          <t>-100,0; 35,01</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,11; 16,15</t>
+          <t>2,5; 15,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 8,48</t>
+          <t>-3,03; 8,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 6,73</t>
+          <t>-6,73; 5,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 8,73</t>
+          <t>-2,53; 8,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 9,33</t>
+          <t>-3,49; 9,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 0,54</t>
+          <t>-9,99; -0,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,44; 10,34</t>
+          <t>1,26; 10,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 7,19</t>
+          <t>-1,55; 7,01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 1,67</t>
+          <t>-6,83; 1,1</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>16,17; 285,28</t>
+          <t>17,39; 254,07</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-30,36; 135,96</t>
+          <t>-30,02; 137,43</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-53,45; 105,53</t>
+          <t>-56,81; 95,67</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,3; 118,08</t>
+          <t>-22,38; 119,51</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-28,1; 122,12</t>
+          <t>-29,68; 129,07</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-74,9; 10,21</t>
+          <t>-73,84; 5,15</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,21; 140,88</t>
+          <t>9,42; 126,76</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 93,45</t>
+          <t>-13,15; 90,77</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-55,13; 20,49</t>
+          <t>-57,69; 16,73</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A05-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A05-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 24,44</t>
+          <t>0,81; 24,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 27,75</t>
+          <t>2,1; 28,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 34,87</t>
+          <t>0,21; 33,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 13,31</t>
+          <t>-14,86; 13,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 23,78</t>
+          <t>-8,0; 23,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,88; -0,89</t>
+          <t>-23,67; -0,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 15,2</t>
+          <t>-2,82; 14,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 21,5</t>
+          <t>0,56; 21,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 11,42</t>
+          <t>-8,23; 11,94</t>
         </is>
       </c>
     </row>
@@ -783,27 +783,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-26,14; 1499,53</t>
+          <t>-11,27; 1260,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 1593,56</t>
+          <t>-23,29; 1460,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-41,87; —</t>
+          <t>-41,89; 1570,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-72,23; 325,8</t>
+          <t>-74,22; 243,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,73; 453,99</t>
+          <t>-50,47; 459,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-22,22; 335,4</t>
+          <t>-28,44; 303,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 428,76</t>
+          <t>-8,8; 455,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-67,54; 231,39</t>
+          <t>-68,97; 286,31</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 18,8</t>
+          <t>-8,22; 17,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 13,25</t>
+          <t>-10,93; 12,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 19,48</t>
+          <t>-10,73; 21,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 13,4</t>
+          <t>-8,51; 13,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 10,44</t>
+          <t>-12,07; 10,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 9,09</t>
+          <t>-13,61; 10,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 11,83</t>
+          <t>-4,39; 12,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 7,53</t>
+          <t>-8,58; 8,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 9,96</t>
+          <t>-8,63; 10,16</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-38,06; 252,76</t>
+          <t>-41,11; 216,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-58,86; 167,07</t>
+          <t>-57,54; 166,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-59,2; 214,88</t>
+          <t>-61,83; 334,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-46,34; 159,11</t>
+          <t>-44,13; 192,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-64,63; 125,71</t>
+          <t>-67,07; 104,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-67,1; 110,16</t>
+          <t>-68,0; 151,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,33; 123,9</t>
+          <t>-28,2; 117,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,99; 72,45</t>
+          <t>-46,25; 85,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-51,18; 96,64</t>
+          <t>-51,63; 95,58</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 25,51</t>
+          <t>-2,27; 25,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,94; 6,91</t>
+          <t>-13,12; 6,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 13,72</t>
+          <t>-9,78; 12,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 15,91</t>
+          <t>-14,19; 16,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 16,23</t>
+          <t>-12,88; 17,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,64; 6,23</t>
+          <t>-19,18; 6,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 15,82</t>
+          <t>-4,15; 15,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 7,86</t>
+          <t>-9,3; 8,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 6,68</t>
+          <t>-10,93; 6,17</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-48,28; —</t>
+          <t>-65,77; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,17 +1225,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-81,84; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-86,23; 380,76</t>
+          <t>-80,29; 498,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-73,99; 390,12</t>
+          <t>-69,08; 431,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-34,42; 393,28</t>
+          <t>-41,17; 361,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-70,43; 218,36</t>
+          <t>-68,34; 213,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-75,52; 168,97</t>
+          <t>-75,3; 153,89</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 24,4</t>
+          <t>-3,75; 23,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 14,3</t>
+          <t>-8,94; 14,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,1; 0,89</t>
+          <t>-14,96; 0,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 11,26</t>
+          <t>-4,97; 12,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 17,1</t>
+          <t>-4,53; 18,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 1,02</t>
+          <t>-8,75; 1,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 14,89</t>
+          <t>-0,8; 15,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 11,32</t>
+          <t>-4,3; 11,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 0,05</t>
+          <t>-8,48; 0,21</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-57,9; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-31,43; 840,45</t>
+          <t>-30,79; 781,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-76,33; 722,66</t>
+          <t>-77,45; 573,72</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 35,01</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,5; 15,44</t>
+          <t>2,68; 15,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 8,47</t>
+          <t>-3,51; 8,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 5,75</t>
+          <t>-6,47; 5,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 8,82</t>
+          <t>-2,99; 9,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 9,57</t>
+          <t>-3,26; 9,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,99; -0,26</t>
+          <t>-10,03; -0,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,26; 10,12</t>
+          <t>0,93; 10,31</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 7,01</t>
+          <t>-1,34; 7,08</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 1,1</t>
+          <t>-6,87; 1,12</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>17,39; 254,07</t>
+          <t>19,25; 250,74</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-30,02; 137,43</t>
+          <t>-31,27; 129,42</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-56,81; 95,67</t>
+          <t>-59,12; 90,58</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-22,38; 119,51</t>
+          <t>-24,43; 117,09</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-29,68; 129,07</t>
+          <t>-27,93; 122,51</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-73,84; 5,15</t>
+          <t>-75,81; 3,34</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,42; 126,76</t>
+          <t>7,04; 139,79</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 90,77</t>
+          <t>-13,16; 88,27</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-57,69; 16,73</t>
+          <t>-57,68; 17,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A05-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A05-Edad-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos antibióticos</t>
+          <t>Menores que consumieron medicamentos antibióticos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,75</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,34</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-9,96</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>11,82</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>13,77</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>14,78</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,75</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,34</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-10,01</t>
+          <t>16,06</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>1,98</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 24,81</t>
+          <t>-12,97; 13,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,1; 28,87</t>
+          <t>-8,56; 22,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 33,96</t>
+          <t>-23,16; -0,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,86; 13,5</t>
+          <t>-0,39; 23,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 23,02</t>
+          <t>1,09; 28,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,67; -0,89</t>
+          <t>-0,17; 36,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 14,94</t>
+          <t>-2,88; 14,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 21,74</t>
+          <t>-0,18; 21,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 11,94</t>
+          <t>-7,46; 13,77</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,31%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>61,64%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-83,64%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>195,33%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>227,7%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>244,26%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,31%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>61,64%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-84,03%</t>
+          <t>265,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 1260,99</t>
+          <t>-69,48; 317,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,29; 1460,18</t>
+          <t>-52,55; 393,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-41,89; 1570,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-74,22; 243,35</t>
+          <t>-30,44; 1104,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,47; 459,56</t>
+          <t>-16,9; 1202,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-47,97; 1665,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-28,44; 303,35</t>
+          <t>-25,17; 333,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 455,81</t>
+          <t>-11,35; 399,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-68,97; 286,31</t>
+          <t>-67,51; 311,02</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,57</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,53</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-1,91</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>5,3</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,56</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,42</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,57</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,53</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-2,25</t>
+          <t>-3,96</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,45</t>
+          <t>-2,92</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 17,75</t>
+          <t>-8,59; 13,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 12,84</t>
+          <t>-12,99; 10,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 21,59</t>
+          <t>-12,0; 11,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 13,91</t>
+          <t>-6,84; 18,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 10,27</t>
+          <t>-10,58; 12,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 10,24</t>
+          <t>-14,96; 6,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 12,29</t>
+          <t>-4,51; 11,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 8,31</t>
+          <t>-8,98; 7,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 10,16</t>
+          <t>-10,25; 4,95</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18,41%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-10,95%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-13,68%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>37,44%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>3,98%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18,41%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-10,95%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-16,09%</t>
+          <t>-27,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-3,23%</t>
+          <t>-20,8%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-41,11; 216,39</t>
+          <t>-46,5; 168,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-57,54; 166,36</t>
+          <t>-65,41; 120,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-61,83; 334,02</t>
+          <t>-64,52; 149,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-44,13; 192,35</t>
+          <t>-37,46; 232,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-67,07; 104,85</t>
+          <t>-55,58; 172,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-68,0; 151,36</t>
+          <t>-71,86; 86,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,2; 117,55</t>
+          <t>-26,77; 120,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,25; 85,37</t>
+          <t>-50,69; 73,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-51,63; 95,58</t>
+          <t>-58,14; 51,37</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,18</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,11</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-4,68</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>11,11</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-0,92</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,73</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,18</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,11</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-5,02</t>
+          <t>2,86</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,34</t>
+          <t>-1,06</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 25,57</t>
+          <t>-14,41; 15,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 6,5</t>
+          <t>-12,67; 15,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 12,45</t>
+          <t>-19,36; 6,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,19; 16,62</t>
+          <t>-2,01; 24,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 17,39</t>
+          <t>-12,82; 6,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,18; 6,12</t>
+          <t>-8,97; 13,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 15,35</t>
+          <t>-4,53; 16,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 8,33</t>
+          <t>-9,47; 8,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 6,17</t>
+          <t>-9,62; 6,82</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18,31%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-40,64%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>193,04%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-16,07%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>47,4%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>18,31%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-43,56%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-15,33%</t>
+          <t>-12,15%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-65,77; —</t>
+          <t>-89,09; 439,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>-71,09; 326,82</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 206,25</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>-60,82; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-80,29; 498,42</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-69,08; 431,57</t>
-        </is>
-      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-87,07; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,17; 361,48</t>
+          <t>-45,14; 368,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-68,34; 213,08</t>
+          <t>-65,86; 275,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-75,3; 153,89</t>
+          <t>-74,83; 188,33</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3,43</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-2,25</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>9,25</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,63</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-4,87</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,9</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,43</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,27</t>
+          <t>-3,82</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-3,33</t>
+          <t>-2,92</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 23,4</t>
+          <t>-4,86; 12,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 14,38</t>
+          <t>-3,33; 19,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,96; 0,66</t>
+          <t>-9,81; 1,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 12,73</t>
+          <t>-2,5; 24,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 18,18</t>
+          <t>-10,14; 14,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 1,02</t>
+          <t>-12,89; 2,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 15,05</t>
+          <t>-1,58; 14,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 11,24</t>
+          <t>-4,82; 10,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 0,21</t>
+          <t>-8,4; 0,66</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>58,9%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>106,19%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-69,73%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>142,27%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>9,77%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-74,95%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>58,9%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>106,19%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-70,26%</t>
+          <t>-58,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-71,53%</t>
+          <t>-62,78%</t>
         </is>
       </c>
     </row>
@@ -1446,32 +1446,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
+          <t>-45,8; —</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-30,79; 781,23</t>
+          <t>-28,5; 779,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-77,45; 573,72</t>
+          <t>-79,73; 433,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 68,19</t>
         </is>
       </c>
     </row>
@@ -1488,47 +1488,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2,75</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2,82</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-4,79</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>8,95</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>2,78</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-0,57</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>5,73</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>2,75</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2,82</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-4,82</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5,73</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2,75</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,7</t>
+          <t>-2,83</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,68; 15,47</t>
+          <t>-2,92; 8,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 8,14</t>
+          <t>-3,61; 9,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 5,85</t>
+          <t>-9,84; 0,55</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 9,2</t>
+          <t>2,11; 16,15</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 9,41</t>
+          <t>-3,3; 8,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,03; -0,02</t>
+          <t>-5,9; 4,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,93; 10,31</t>
+          <t>1,44; 10,34</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 7,08</t>
+          <t>-1,81; 7,19</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 1,12</t>
+          <t>-6,46; 0,75</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>26,99%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>27,68%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-46,91%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>100,58%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>31,27%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-5,1%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>26,99%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>27,68%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-47,29%</t>
+          <t>-6,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-28,17%</t>
+          <t>-29,46%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>19,25; 250,74</t>
+          <t>-24,3; 118,08</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-31,27; 129,42</t>
+          <t>-28,1; 122,12</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-59,12; 90,58</t>
+          <t>-74,88; 12,87</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,43; 117,09</t>
+          <t>16,17; 285,28</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-27,93; 122,51</t>
+          <t>-30,36; 135,96</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-75,81; 3,34</t>
+          <t>-50,1; 81,93</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,04; 139,79</t>
+          <t>12,21; 140,88</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 88,27</t>
+          <t>-15,71; 93,45</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-57,68; 17,04</t>
+          <t>-55,67; 12,39</t>
         </is>
       </c>
     </row>
